--- a/capacidad_baterias.xlsx
+++ b/capacidad_baterias.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ce3gk\OneDrive\Escritorio\opti\proyecto\ics1113_proyecto_grupo03\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\OneDrive\Documentos\UC\Semester 6\OPTI\tarea\Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098F641E-D6D3-43A9-AF8E-C5C439AACAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6EFFCA-49B4-4554-8E9C-FAF8604CB477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t" sheetId="1" r:id="rId1"/>
-    <sheet name="t1000" sheetId="2" r:id="rId2"/>
+    <sheet name="t_chico" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,8 +47,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -76,8 +84,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,12 +422,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -426,7 +435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -434,7 +443,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -449,10 +458,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EF02E72-F9FE-44C3-B225-DEBD587AC1B0}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -460,21 +469,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6900</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8000</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
